--- a/static/data/exports/Retro_HP_AE_2022.xlsx
+++ b/static/data/exports/Retro_HP_AE_2022.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -576,8 +576,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>39</v>
+      </c>
       <c r="Q2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>45</v>
@@ -638,6 +651,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>43</v>
+      </c>
       <c r="Q3" t="b">
         <v>0</v>
       </c>
@@ -762,6 +788,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>35</v>
+      </c>
       <c r="Q5" t="b">
         <v>0</v>
       </c>
@@ -824,6 +863,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>43</v>
+      </c>
       <c r="Q6" t="b">
         <v>0</v>
       </c>
@@ -886,6 +938,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>75</v>
+      </c>
       <c r="Q7" t="b">
         <v>0</v>
       </c>
@@ -1010,6 +1075,19 @@
           <t>HIMJKP</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>29</v>
+      </c>
       <c r="Q9" t="b">
         <v>0</v>
       </c>
@@ -1072,6 +1150,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>58</v>
+      </c>
       <c r="Q10" t="b">
         <v>0</v>
       </c>
@@ -1134,6 +1225,19 @@
           <t>HCHLJP</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>48</v>
+      </c>
       <c r="Q11" t="b">
         <v>0</v>
       </c>
@@ -1196,6 +1300,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>51</v>
+      </c>
       <c r="Q12" t="b">
         <v>0</v>
       </c>
@@ -1258,6 +1375,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>60</v>
+      </c>
       <c r="Q13" t="b">
         <v>0</v>
       </c>
@@ -1320,6 +1450,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>47</v>
+      </c>
       <c r="Q14" t="b">
         <v>0</v>
       </c>
@@ -1444,6 +1587,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>39</v>
+      </c>
       <c r="Q16" t="b">
         <v>0</v>
       </c>
@@ -1506,6 +1662,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>49</v>
+      </c>
       <c r="Q17" t="b">
         <v>0</v>
       </c>
@@ -1568,6 +1737,19 @@
           <t>BVD</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>34</v>
+      </c>
       <c r="Q18" t="b">
         <v>0</v>
       </c>
@@ -1630,6 +1812,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>55</v>
+      </c>
       <c r="Q19" t="b">
         <v>0</v>
       </c>
@@ -1692,8 +1887,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>67</v>
+      </c>
       <c r="Q20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>45</v>
@@ -1816,6 +2024,19 @@
           <t>RTRYDVBHMP</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>54</v>
+      </c>
       <c r="Q22" t="b">
         <v>0</v>
       </c>
@@ -1878,6 +2099,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>35</v>
+      </c>
       <c r="Q23" t="b">
         <v>0</v>
       </c>
@@ -1940,6 +2174,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>34</v>
+      </c>
       <c r="Q24" t="b">
         <v>0</v>
       </c>
@@ -2002,6 +2249,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>65</v>
+      </c>
       <c r="Q25" t="b">
         <v>0</v>
       </c>
@@ -2064,8 +2324,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>61</v>
+      </c>
       <c r="Q26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
         <v>45</v>
@@ -2126,6 +2399,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>39</v>
+      </c>
       <c r="Q27" t="b">
         <v>0</v>
       </c>
@@ -2188,6 +2474,19 @@
           <t>HSP</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>35</v>
+      </c>
       <c r="Q28" t="b">
         <v>0</v>
       </c>
@@ -2312,6 +2611,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>45</v>
+      </c>
       <c r="Q30" t="b">
         <v>0</v>
       </c>
@@ -2374,6 +2686,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>44</v>
+      </c>
       <c r="Q31" t="b">
         <v>0</v>
       </c>
@@ -2436,6 +2761,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>64</v>
+      </c>
       <c r="Q32" t="b">
         <v>0</v>
       </c>
@@ -2498,6 +2836,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>56</v>
+      </c>
       <c r="Q33" t="b">
         <v>0</v>
       </c>
@@ -2622,6 +2973,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>30</v>
+      </c>
       <c r="Q35" t="b">
         <v>0</v>
       </c>
@@ -2684,6 +3048,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>66</v>
+      </c>
       <c r="Q36" t="b">
         <v>0</v>
       </c>
@@ -2746,6 +3123,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>49</v>
+      </c>
       <c r="Q37" t="b">
         <v>0</v>
       </c>
@@ -2808,8 +3198,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>47</v>
+      </c>
       <c r="Q38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
         <v>45</v>
@@ -2870,6 +3273,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>63</v>
+      </c>
       <c r="Q39" t="b">
         <v>0</v>
       </c>
@@ -2932,6 +3348,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>46</v>
+      </c>
       <c r="Q40" t="b">
         <v>0</v>
       </c>
@@ -2994,6 +3423,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>48</v>
+      </c>
       <c r="Q41" t="b">
         <v>0</v>
       </c>
@@ -3118,6 +3560,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>72</v>
+      </c>
       <c r="Q43" t="b">
         <v>0</v>
       </c>
@@ -3180,6 +3635,19 @@
           <t>HSP</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>34</v>
+      </c>
       <c r="Q44" t="b">
         <v>0</v>
       </c>
@@ -3242,6 +3710,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>48</v>
+      </c>
       <c r="Q45" t="b">
         <v>0</v>
       </c>
@@ -3304,6 +3785,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>58</v>
+      </c>
       <c r="Q46" t="b">
         <v>0</v>
       </c>
@@ -3366,6 +3860,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>63</v>
+      </c>
       <c r="Q47" t="b">
         <v>0</v>
       </c>
@@ -3428,6 +3935,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>67</v>
+      </c>
       <c r="Q48" t="b">
         <v>0</v>
       </c>
@@ -3490,6 +4010,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>30</v>
+      </c>
       <c r="Q49" t="b">
         <v>0</v>
       </c>
@@ -3614,6 +4147,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>64</v>
+      </c>
       <c r="Q51" t="b">
         <v>0</v>
       </c>
@@ -3676,6 +4222,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>55</v>
+      </c>
       <c r="Q52" t="b">
         <v>0</v>
       </c>
@@ -3738,6 +4297,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>63</v>
+      </c>
       <c r="Q53" t="b">
         <v>0</v>
       </c>
@@ -3800,6 +4372,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>78</v>
+      </c>
       <c r="Q54" t="b">
         <v>0</v>
       </c>
@@ -3862,6 +4447,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>60</v>
+      </c>
       <c r="Q55" t="b">
         <v>0</v>
       </c>
@@ -3986,6 +4584,19 @@
           <t>HIMJKP</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>42</v>
+      </c>
       <c r="Q57" t="b">
         <v>0</v>
       </c>
@@ -4048,6 +4659,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>62</v>
+      </c>
       <c r="Q58" t="b">
         <v>0</v>
       </c>
@@ -4110,6 +4734,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>69</v>
+      </c>
       <c r="Q59" t="b">
         <v>0</v>
       </c>
@@ -4172,8 +4809,21 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>56</v>
+      </c>
       <c r="Q60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R60" t="n">
         <v>45</v>
@@ -4234,6 +4884,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>56</v>
+      </c>
       <c r="Q61" t="b">
         <v>0</v>
       </c>
@@ -4296,6 +4959,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>71</v>
+      </c>
       <c r="Q62" t="b">
         <v>0</v>
       </c>
@@ -4358,6 +5034,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>26</v>
+      </c>
       <c r="Q63" t="b">
         <v>0</v>
       </c>
@@ -4420,6 +5109,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>46</v>
+      </c>
       <c r="Q64" t="b">
         <v>0</v>
       </c>
@@ -4544,6 +5246,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>60</v>
+      </c>
       <c r="Q66" t="b">
         <v>0</v>
       </c>
@@ -4606,8 +5321,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>58</v>
+      </c>
       <c r="Q67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R67" t="n">
         <v>45</v>
@@ -4668,6 +5396,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>58</v>
+      </c>
       <c r="Q68" t="b">
         <v>0</v>
       </c>
@@ -4730,6 +5471,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>51</v>
+      </c>
       <c r="Q69" t="b">
         <v>0</v>
       </c>
@@ -4792,6 +5546,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>40</v>
+      </c>
       <c r="Q70" t="b">
         <v>0</v>
       </c>
@@ -4916,6 +5683,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>61</v>
+      </c>
       <c r="Q72" t="b">
         <v>0</v>
       </c>
@@ -4978,6 +5758,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>26</v>
+      </c>
       <c r="Q73" t="b">
         <v>0</v>
       </c>
@@ -5040,6 +5833,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>59</v>
+      </c>
       <c r="Q74" t="b">
         <v>0</v>
       </c>
@@ -5102,6 +5908,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>67</v>
+      </c>
       <c r="Q75" t="b">
         <v>0</v>
       </c>
@@ -5164,6 +5983,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>40</v>
+      </c>
       <c r="Q76" t="b">
         <v>0</v>
       </c>
@@ -5226,6 +6058,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>58</v>
+      </c>
       <c r="Q77" t="b">
         <v>0</v>
       </c>
@@ -5243,20 +6088,20 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1945411</v>
+        <v>1945410</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Sushil Kumar</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BSP</t>
+          <t>NOTA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>16537</v>
+        <v>16540</v>
       </c>
       <c r="E78" t="n">
         <v>201</v>
@@ -5280,12 +6125,12 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Sushil Kumar</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>BSP</t>
+          <t>NOTA</t>
         </is>
       </c>
       <c r="Q78" t="b">
@@ -5305,20 +6150,20 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1945410</v>
+        <v>1945411</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Sushil Kumar</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NOTA</t>
+          <t>BSP</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>16540</v>
+        <v>16537</v>
       </c>
       <c r="E79" t="n">
         <v>201</v>
@@ -5342,13 +6187,26 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Sushil Kumar</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>NOTA</t>
-        </is>
+          <t>BSP</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>43</v>
       </c>
       <c r="Q79" t="b">
         <v>0</v>
@@ -5412,6 +6270,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>46</v>
+      </c>
       <c r="Q80" t="b">
         <v>0</v>
       </c>
@@ -5474,6 +6345,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>36</v>
+      </c>
       <c r="Q81" t="b">
         <v>0</v>
       </c>
@@ -5536,6 +6420,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>61</v>
+      </c>
       <c r="Q82" t="b">
         <v>0</v>
       </c>
@@ -5598,6 +6495,19 @@
           <t>RTRYDVBHMP</t>
         </is>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>47</v>
+      </c>
       <c r="Q83" t="b">
         <v>0</v>
       </c>
@@ -5660,6 +6570,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>49</v>
+      </c>
       <c r="Q84" t="b">
         <v>0</v>
       </c>
@@ -5784,6 +6707,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>37</v>
+      </c>
       <c r="Q86" t="b">
         <v>0</v>
       </c>
@@ -5846,6 +6782,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>52</v>
+      </c>
       <c r="Q87" t="b">
         <v>0</v>
       </c>
@@ -5908,8 +6857,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>59</v>
+      </c>
       <c r="Q88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R88" t="n">
         <v>45</v>
@@ -5970,6 +6932,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>68</v>
+      </c>
       <c r="Q89" t="b">
         <v>0</v>
       </c>
@@ -6032,6 +7007,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>67</v>
+      </c>
       <c r="Q90" t="b">
         <v>0</v>
       </c>
@@ -6094,6 +7082,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>56</v>
+      </c>
       <c r="Q91" t="b">
         <v>0</v>
       </c>
@@ -6156,6 +7157,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>56</v>
+      </c>
       <c r="Q92" t="b">
         <v>0</v>
       </c>
@@ -6280,6 +7294,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>27</v>
+      </c>
       <c r="Q94" t="b">
         <v>0</v>
       </c>
@@ -6342,6 +7369,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>40</v>
+      </c>
       <c r="Q95" t="b">
         <v>0</v>
       </c>
@@ -6404,6 +7444,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>37</v>
+      </c>
       <c r="Q96" t="b">
         <v>0</v>
       </c>
@@ -6466,6 +7519,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>62</v>
+      </c>
       <c r="Q97" t="b">
         <v>0</v>
       </c>
@@ -6528,6 +7594,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>43</v>
+      </c>
       <c r="Q98" t="b">
         <v>0</v>
       </c>
@@ -6590,6 +7669,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>58</v>
+      </c>
       <c r="Q99" t="b">
         <v>0</v>
       </c>
@@ -6652,6 +7744,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>43</v>
+      </c>
       <c r="Q100" t="b">
         <v>0</v>
       </c>
@@ -6776,6 +7881,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>40</v>
+      </c>
       <c r="Q102" t="b">
         <v>0</v>
       </c>
@@ -6838,6 +7956,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>48</v>
+      </c>
       <c r="Q103" t="b">
         <v>0</v>
       </c>
@@ -6900,6 +8031,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>68</v>
+      </c>
       <c r="Q104" t="b">
         <v>0</v>
       </c>
@@ -6962,6 +8106,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>58</v>
+      </c>
       <c r="Q105" t="b">
         <v>0</v>
       </c>
@@ -7024,6 +8181,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>45</v>
+      </c>
       <c r="Q106" t="b">
         <v>0</v>
       </c>
@@ -7086,6 +8256,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>68</v>
+      </c>
       <c r="Q107" t="b">
         <v>0</v>
       </c>
@@ -7210,6 +8393,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P109" t="n">
+        <v>59</v>
+      </c>
       <c r="Q109" t="b">
         <v>0</v>
       </c>
@@ -7272,6 +8468,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>53</v>
+      </c>
       <c r="Q110" t="b">
         <v>0</v>
       </c>
@@ -7334,6 +8543,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P111" t="n">
+        <v>56</v>
+      </c>
       <c r="Q111" t="b">
         <v>0</v>
       </c>
@@ -7396,6 +8618,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P112" t="n">
+        <v>30</v>
+      </c>
       <c r="Q112" t="b">
         <v>0</v>
       </c>
@@ -7458,6 +8693,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P113" t="n">
+        <v>44</v>
+      </c>
       <c r="Q113" t="b">
         <v>0</v>
       </c>
@@ -7582,6 +8830,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P115" t="n">
+        <v>33</v>
+      </c>
       <c r="Q115" t="b">
         <v>0</v>
       </c>
@@ -7644,6 +8905,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P116" t="n">
+        <v>61</v>
+      </c>
       <c r="Q116" t="b">
         <v>0</v>
       </c>
@@ -7706,6 +8980,19 @@
           <t>HSP</t>
         </is>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P117" t="n">
+        <v>30</v>
+      </c>
       <c r="Q117" t="b">
         <v>0</v>
       </c>
@@ -7768,6 +9055,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P118" t="n">
+        <v>50</v>
+      </c>
       <c r="Q118" t="b">
         <v>0</v>
       </c>
@@ -7830,6 +9130,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P119" t="n">
+        <v>44</v>
+      </c>
       <c r="Q119" t="b">
         <v>0</v>
       </c>
@@ -7892,6 +9205,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P120" t="n">
+        <v>37</v>
+      </c>
       <c r="Q120" t="b">
         <v>0</v>
       </c>
@@ -7954,6 +9280,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P121" t="n">
+        <v>67</v>
+      </c>
       <c r="Q121" t="b">
         <v>0</v>
       </c>
@@ -8078,6 +9417,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>69</v>
+      </c>
       <c r="Q123" t="b">
         <v>0</v>
       </c>
@@ -8140,6 +9492,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P124" t="n">
+        <v>62</v>
+      </c>
       <c r="Q124" t="b">
         <v>0</v>
       </c>
@@ -8202,8 +9567,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P125" t="n">
+        <v>42</v>
+      </c>
       <c r="Q125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R125" t="n">
         <v>45</v>
@@ -8264,6 +9642,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P126" t="n">
+        <v>54</v>
+      </c>
       <c r="Q126" t="b">
         <v>0</v>
       </c>
@@ -8326,6 +9717,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P127" t="n">
+        <v>52</v>
+      </c>
       <c r="Q127" t="b">
         <v>0</v>
       </c>
@@ -8450,6 +9854,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>48</v>
+      </c>
       <c r="Q129" t="b">
         <v>0</v>
       </c>
@@ -8512,6 +9929,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>75</v>
+      </c>
       <c r="Q130" t="b">
         <v>0</v>
       </c>
@@ -8574,6 +10004,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>52</v>
+      </c>
       <c r="Q131" t="b">
         <v>0</v>
       </c>
@@ -8636,6 +10079,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>48</v>
+      </c>
       <c r="Q132" t="b">
         <v>0</v>
       </c>
@@ -8760,6 +10216,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>47</v>
+      </c>
       <c r="Q134" t="b">
         <v>0</v>
       </c>
@@ -8822,6 +10291,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
+        <v>50</v>
+      </c>
       <c r="Q135" t="b">
         <v>0</v>
       </c>
@@ -8884,6 +10366,19 @@
           <t>SWAP</t>
         </is>
       </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P136" t="n">
+        <v>38</v>
+      </c>
       <c r="Q136" t="b">
         <v>0</v>
       </c>
@@ -8946,6 +10441,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P137" t="n">
+        <v>60</v>
+      </c>
       <c r="Q137" t="b">
         <v>0</v>
       </c>
@@ -9008,8 +10516,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P138" t="n">
+        <v>56</v>
+      </c>
       <c r="Q138" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R138" t="n">
         <v>45</v>
@@ -9070,6 +10591,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P139" t="n">
+        <v>41</v>
+      </c>
       <c r="Q139" t="b">
         <v>0</v>
       </c>
@@ -9194,6 +10728,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P141" t="n">
+        <v>48</v>
+      </c>
       <c r="Q141" t="b">
         <v>0</v>
       </c>
@@ -9256,8 +10803,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P142" t="n">
+        <v>54</v>
+      </c>
       <c r="Q142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R142" t="n">
         <v>45</v>
@@ -9318,6 +10878,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P143" t="n">
+        <v>46</v>
+      </c>
       <c r="Q143" t="b">
         <v>0</v>
       </c>
@@ -9380,6 +10953,19 @@
           <t>RTRYDVBHMP</t>
         </is>
       </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>43</v>
+      </c>
       <c r="Q144" t="b">
         <v>0</v>
       </c>
@@ -9442,6 +11028,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>51</v>
+      </c>
       <c r="Q145" t="b">
         <v>0</v>
       </c>
@@ -9504,6 +11103,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>57</v>
+      </c>
       <c r="Q146" t="b">
         <v>0</v>
       </c>
@@ -9628,8 +11240,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P148" t="n">
+        <v>57</v>
+      </c>
       <c r="Q148" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R148" t="n">
         <v>45</v>
@@ -9690,6 +11315,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P149" t="n">
+        <v>55</v>
+      </c>
       <c r="Q149" t="b">
         <v>0</v>
       </c>
@@ -9752,6 +11390,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P150" t="n">
+        <v>62</v>
+      </c>
       <c r="Q150" t="b">
         <v>0</v>
       </c>
@@ -9814,6 +11465,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>47</v>
+      </c>
       <c r="Q151" t="b">
         <v>0</v>
       </c>
@@ -9876,6 +11540,19 @@
           <t>CPI(M)</t>
         </is>
       </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P152" t="n">
+        <v>54</v>
+      </c>
       <c r="Q152" t="b">
         <v>0</v>
       </c>
@@ -10000,6 +11677,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P154" t="n">
+        <v>53</v>
+      </c>
       <c r="Q154" t="b">
         <v>0</v>
       </c>
@@ -10062,8 +11752,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P155" t="n">
+        <v>41</v>
+      </c>
       <c r="Q155" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R155" t="n">
         <v>45</v>
@@ -10124,6 +11827,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P156" t="n">
+        <v>73</v>
+      </c>
       <c r="Q156" t="b">
         <v>0</v>
       </c>
@@ -10186,6 +11902,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P157" t="n">
+        <v>48</v>
+      </c>
       <c r="Q157" t="b">
         <v>0</v>
       </c>
@@ -10310,6 +12039,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P159" t="n">
+        <v>52</v>
+      </c>
       <c r="Q159" t="b">
         <v>0</v>
       </c>
@@ -10372,6 +12114,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P160" t="n">
+        <v>44</v>
+      </c>
       <c r="Q160" t="b">
         <v>0</v>
       </c>
@@ -10434,6 +12189,19 @@
           <t>HIMJKP</t>
         </is>
       </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P161" t="n">
+        <v>48</v>
+      </c>
       <c r="Q161" t="b">
         <v>0</v>
       </c>
@@ -10496,6 +12264,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P162" t="n">
+        <v>34</v>
+      </c>
       <c r="Q162" t="b">
         <v>0</v>
       </c>
@@ -10558,6 +12339,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P163" t="n">
+        <v>49</v>
+      </c>
       <c r="Q163" t="b">
         <v>0</v>
       </c>
@@ -10620,6 +12414,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P164" t="n">
+        <v>55</v>
+      </c>
       <c r="Q164" t="b">
         <v>0</v>
       </c>
@@ -10682,6 +12489,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P165" t="n">
+        <v>52</v>
+      </c>
       <c r="Q165" t="b">
         <v>0</v>
       </c>
@@ -10744,6 +12564,19 @@
           <t>CPI(M)</t>
         </is>
       </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P166" t="n">
+        <v>45</v>
+      </c>
       <c r="Q166" t="b">
         <v>0</v>
       </c>
@@ -10806,6 +12639,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P167" t="n">
+        <v>40</v>
+      </c>
       <c r="Q167" t="b">
         <v>0</v>
       </c>
@@ -10930,6 +12776,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P169" t="n">
+        <v>34</v>
+      </c>
       <c r="Q169" t="b">
         <v>0</v>
       </c>
@@ -10992,6 +12851,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P170" t="n">
+        <v>51</v>
+      </c>
       <c r="Q170" t="b">
         <v>0</v>
       </c>
@@ -11054,6 +12926,19 @@
           <t>CPI(M)</t>
         </is>
       </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P171" t="n">
+        <v>31</v>
+      </c>
       <c r="Q171" t="b">
         <v>0</v>
       </c>
@@ -11116,6 +13001,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P172" t="n">
+        <v>57</v>
+      </c>
       <c r="Q172" t="b">
         <v>0</v>
       </c>
@@ -11240,6 +13138,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P174" t="n">
+        <v>55</v>
+      </c>
       <c r="Q174" t="b">
         <v>0</v>
       </c>
@@ -11302,6 +13213,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P175" t="n">
+        <v>35</v>
+      </c>
       <c r="Q175" t="b">
         <v>0</v>
       </c>
@@ -11364,6 +13288,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P176" t="n">
+        <v>48</v>
+      </c>
       <c r="Q176" t="b">
         <v>0</v>
       </c>
@@ -11426,6 +13363,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P177" t="n">
+        <v>64</v>
+      </c>
       <c r="Q177" t="b">
         <v>0</v>
       </c>
@@ -11488,6 +13438,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P178" t="n">
+        <v>47</v>
+      </c>
       <c r="Q178" t="b">
         <v>0</v>
       </c>
@@ -11550,6 +13513,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P179" t="n">
+        <v>35</v>
+      </c>
       <c r="Q179" t="b">
         <v>0</v>
       </c>
@@ -11674,6 +13650,19 @@
           <t>SaSP</t>
         </is>
       </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P181" t="n">
+        <v>69</v>
+      </c>
       <c r="Q181" t="b">
         <v>0</v>
       </c>
@@ -11736,6 +13725,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P182" t="n">
+        <v>61</v>
+      </c>
       <c r="Q182" t="b">
         <v>0</v>
       </c>
@@ -11798,6 +13800,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P183" t="n">
+        <v>31</v>
+      </c>
       <c r="Q183" t="b">
         <v>0</v>
       </c>
@@ -11860,6 +13875,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P184" t="n">
+        <v>42</v>
+      </c>
       <c r="Q184" t="b">
         <v>0</v>
       </c>
@@ -11922,6 +13950,19 @@
           <t>RTRYDVBHMP</t>
         </is>
       </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P185" t="n">
+        <v>36</v>
+      </c>
       <c r="Q185" t="b">
         <v>0</v>
       </c>
@@ -11984,8 +14025,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P186" t="n">
+        <v>42</v>
+      </c>
       <c r="Q186" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R186" t="n">
         <v>45</v>
@@ -12046,6 +14100,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P187" t="n">
+        <v>47</v>
+      </c>
       <c r="Q187" t="b">
         <v>0</v>
       </c>
@@ -12108,6 +14175,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P188" t="n">
+        <v>44</v>
+      </c>
       <c r="Q188" t="b">
         <v>0</v>
       </c>
@@ -12170,6 +14250,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P189" t="n">
+        <v>31</v>
+      </c>
       <c r="Q189" t="b">
         <v>0</v>
       </c>
@@ -12294,6 +14387,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P191" t="n">
+        <v>49</v>
+      </c>
       <c r="Q191" t="b">
         <v>0</v>
       </c>
@@ -12356,6 +14462,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P192" t="n">
+        <v>29</v>
+      </c>
       <c r="Q192" t="b">
         <v>0</v>
       </c>
@@ -12418,6 +14537,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P193" t="n">
+        <v>62</v>
+      </c>
       <c r="Q193" t="b">
         <v>0</v>
       </c>
@@ -12480,8 +14612,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P194" t="n">
+        <v>57</v>
+      </c>
       <c r="Q194" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R194" t="n">
         <v>45</v>
@@ -12542,6 +14687,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P195" t="n">
+        <v>62</v>
+      </c>
       <c r="Q195" t="b">
         <v>0</v>
       </c>
@@ -12604,6 +14762,19 @@
           <t>CPI(M)</t>
         </is>
       </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P196" t="n">
+        <v>40</v>
+      </c>
       <c r="Q196" t="b">
         <v>0</v>
       </c>
@@ -12666,6 +14837,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P197" t="n">
+        <v>61</v>
+      </c>
       <c r="Q197" t="b">
         <v>0</v>
       </c>
@@ -12790,6 +14974,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P199" t="n">
+        <v>53</v>
+      </c>
       <c r="Q199" t="b">
         <v>0</v>
       </c>
@@ -12852,6 +15049,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P200" t="n">
+        <v>35</v>
+      </c>
       <c r="Q200" t="b">
         <v>0</v>
       </c>
@@ -12914,6 +15124,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P201" t="n">
+        <v>65</v>
+      </c>
       <c r="Q201" t="b">
         <v>0</v>
       </c>
@@ -12976,6 +15199,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P202" t="n">
+        <v>76</v>
+      </c>
       <c r="Q202" t="b">
         <v>0</v>
       </c>
@@ -13100,6 +15336,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P204" t="n">
+        <v>34</v>
+      </c>
       <c r="Q204" t="b">
         <v>0</v>
       </c>
@@ -13162,6 +15411,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P205" t="n">
+        <v>60</v>
+      </c>
       <c r="Q205" t="b">
         <v>0</v>
       </c>
@@ -13224,6 +15486,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P206" t="n">
+        <v>62</v>
+      </c>
       <c r="Q206" t="b">
         <v>0</v>
       </c>
@@ -13286,6 +15561,19 @@
           <t>CPI(M)</t>
         </is>
       </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P207" t="n">
+        <v>53</v>
+      </c>
       <c r="Q207" t="b">
         <v>0</v>
       </c>
@@ -13348,6 +15636,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P208" t="n">
+        <v>48</v>
+      </c>
       <c r="Q208" t="b">
         <v>0</v>
       </c>
@@ -13410,6 +15711,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P209" t="n">
+        <v>51</v>
+      </c>
       <c r="Q209" t="b">
         <v>0</v>
       </c>
@@ -13534,6 +15848,19 @@
           <t>RTRYDVBHMP</t>
         </is>
       </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P211" t="n">
+        <v>48</v>
+      </c>
       <c r="Q211" t="b">
         <v>0</v>
       </c>
@@ -13596,6 +15923,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P212" t="n">
+        <v>47</v>
+      </c>
       <c r="Q212" t="b">
         <v>0</v>
       </c>
@@ -13658,6 +15998,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P213" t="n">
+        <v>64</v>
+      </c>
       <c r="Q213" t="b">
         <v>0</v>
       </c>
@@ -13720,6 +16073,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P214" t="n">
+        <v>74</v>
+      </c>
       <c r="Q214" t="b">
         <v>0</v>
       </c>
@@ -13782,6 +16148,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P215" t="n">
+        <v>42</v>
+      </c>
       <c r="Q215" t="b">
         <v>0</v>
       </c>
@@ -13844,6 +16223,19 @@
           <t>RSHTLKNTP</t>
         </is>
       </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P216" t="n">
+        <v>67</v>
+      </c>
       <c r="Q216" t="b">
         <v>0</v>
       </c>
@@ -13906,6 +16298,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P217" t="n">
+        <v>49</v>
+      </c>
       <c r="Q217" t="b">
         <v>0</v>
       </c>
@@ -13968,6 +16373,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P218" t="n">
+        <v>45</v>
+      </c>
       <c r="Q218" t="b">
         <v>0</v>
       </c>
@@ -14030,6 +16448,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P219" t="n">
+        <v>42</v>
+      </c>
       <c r="Q219" t="b">
         <v>0</v>
       </c>
@@ -14154,6 +16585,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P221" t="n">
+        <v>64</v>
+      </c>
       <c r="Q221" t="b">
         <v>0</v>
       </c>
@@ -14216,6 +16660,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P222" t="n">
+        <v>49</v>
+      </c>
       <c r="Q222" t="b">
         <v>0</v>
       </c>
@@ -14278,8 +16735,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P223" t="n">
+        <v>66</v>
+      </c>
       <c r="Q223" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R223" t="n">
         <v>45</v>
@@ -14340,6 +16810,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P224" t="n">
+        <v>48</v>
+      </c>
       <c r="Q224" t="b">
         <v>0</v>
       </c>
@@ -14402,6 +16885,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P225" t="n">
+        <v>46</v>
+      </c>
       <c r="Q225" t="b">
         <v>0</v>
       </c>
@@ -14464,6 +16960,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P226" t="n">
+        <v>52</v>
+      </c>
       <c r="Q226" t="b">
         <v>0</v>
       </c>
@@ -14588,6 +17097,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P228" t="n">
+        <v>49</v>
+      </c>
       <c r="Q228" t="b">
         <v>0</v>
       </c>
@@ -14650,6 +17172,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P229" t="n">
+        <v>34</v>
+      </c>
       <c r="Q229" t="b">
         <v>0</v>
       </c>
@@ -14712,6 +17247,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P230" t="n">
+        <v>51</v>
+      </c>
       <c r="Q230" t="b">
         <v>0</v>
       </c>
@@ -14774,6 +17322,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P231" t="n">
+        <v>56</v>
+      </c>
       <c r="Q231" t="b">
         <v>0</v>
       </c>
@@ -14836,6 +17397,19 @@
           <t>RTRYDVBHMP</t>
         </is>
       </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P232" t="n">
+        <v>34</v>
+      </c>
       <c r="Q232" t="b">
         <v>0</v>
       </c>
@@ -14898,8 +17472,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P233" t="n">
+        <v>60</v>
+      </c>
       <c r="Q233" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R233" t="n">
         <v>45</v>
@@ -14960,6 +17547,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P234" t="n">
+        <v>60</v>
+      </c>
       <c r="Q234" t="b">
         <v>0</v>
       </c>
@@ -15022,6 +17622,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P235" t="n">
+        <v>60</v>
+      </c>
       <c r="Q235" t="b">
         <v>0</v>
       </c>
@@ -15146,6 +17759,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P237" t="n">
+        <v>45</v>
+      </c>
       <c r="Q237" t="b">
         <v>0</v>
       </c>
@@ -15208,6 +17834,19 @@
           <t>RTRYDVBHMP</t>
         </is>
       </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P238" t="n">
+        <v>45</v>
+      </c>
       <c r="Q238" t="b">
         <v>0</v>
       </c>
@@ -15270,6 +17909,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P239" t="n">
+        <v>57</v>
+      </c>
       <c r="Q239" t="b">
         <v>0</v>
       </c>
@@ -15332,6 +17984,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P240" t="n">
+        <v>48</v>
+      </c>
       <c r="Q240" t="b">
         <v>0</v>
       </c>
@@ -15394,6 +18059,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P241" t="n">
+        <v>38</v>
+      </c>
       <c r="Q241" t="b">
         <v>0</v>
       </c>
@@ -15518,6 +18196,19 @@
           <t>RTRYDVBHMP</t>
         </is>
       </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P243" t="n">
+        <v>32</v>
+      </c>
       <c r="Q243" t="b">
         <v>0</v>
       </c>
@@ -15580,6 +18271,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P244" t="n">
+        <v>47</v>
+      </c>
       <c r="Q244" t="b">
         <v>0</v>
       </c>
@@ -15642,6 +18346,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P245" t="n">
+        <v>53</v>
+      </c>
       <c r="Q245" t="b">
         <v>0</v>
       </c>
@@ -15704,6 +18421,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P246" t="n">
+        <v>55</v>
+      </c>
       <c r="Q246" t="b">
         <v>0</v>
       </c>
@@ -15766,6 +18496,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P247" t="n">
+        <v>59</v>
+      </c>
       <c r="Q247" t="b">
         <v>0</v>
       </c>
@@ -15828,6 +18571,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P248" t="n">
+        <v>48</v>
+      </c>
       <c r="Q248" t="b">
         <v>0</v>
       </c>
@@ -15890,6 +18646,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P249" t="n">
+        <v>49</v>
+      </c>
       <c r="Q249" t="b">
         <v>0</v>
       </c>
@@ -15952,6 +18721,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P250" t="n">
+        <v>63</v>
+      </c>
       <c r="Q250" t="b">
         <v>0</v>
       </c>
@@ -16076,8 +18858,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P252" t="n">
+        <v>56</v>
+      </c>
       <c r="Q252" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R252" t="n">
         <v>45</v>
@@ -16138,6 +18933,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P253" t="n">
+        <v>65</v>
+      </c>
       <c r="Q253" t="b">
         <v>0</v>
       </c>
@@ -16262,6 +19070,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P255" t="n">
+        <v>31</v>
+      </c>
       <c r="Q255" t="b">
         <v>0</v>
       </c>
@@ -16324,6 +19145,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P256" t="n">
+        <v>68</v>
+      </c>
       <c r="Q256" t="b">
         <v>0</v>
       </c>
@@ -16386,6 +19220,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P257" t="n">
+        <v>47</v>
+      </c>
       <c r="Q257" t="b">
         <v>0</v>
       </c>
@@ -16448,6 +19295,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P258" t="n">
+        <v>35</v>
+      </c>
       <c r="Q258" t="b">
         <v>0</v>
       </c>
@@ -16510,6 +19370,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P259" t="n">
+        <v>47</v>
+      </c>
       <c r="Q259" t="b">
         <v>0</v>
       </c>
@@ -16572,8 +19445,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P260" t="n">
+        <v>65</v>
+      </c>
       <c r="Q260" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R260" t="n">
         <v>45</v>
@@ -16634,6 +19520,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P261" t="n">
+        <v>54</v>
+      </c>
       <c r="Q261" t="b">
         <v>0</v>
       </c>
@@ -16696,6 +19595,19 @@
           <t>CPI(M)</t>
         </is>
       </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P262" t="n">
+        <v>68</v>
+      </c>
       <c r="Q262" t="b">
         <v>0</v>
       </c>
@@ -16758,6 +19670,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P263" t="n">
+        <v>42</v>
+      </c>
       <c r="Q263" t="b">
         <v>0</v>
       </c>
@@ -16820,6 +19745,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P264" t="n">
+        <v>64</v>
+      </c>
       <c r="Q264" t="b">
         <v>0</v>
       </c>
@@ -16944,6 +19882,19 @@
           <t>RTRYDVBHMP</t>
         </is>
       </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P266" t="n">
+        <v>40</v>
+      </c>
       <c r="Q266" t="b">
         <v>0</v>
       </c>
@@ -17006,6 +19957,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P267" t="n">
+        <v>45</v>
+      </c>
       <c r="Q267" t="b">
         <v>0</v>
       </c>
@@ -17068,8 +20032,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P268" t="n">
+        <v>60</v>
+      </c>
       <c r="Q268" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R268" t="n">
         <v>45</v>
@@ -17130,6 +20107,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P269" t="n">
+        <v>52</v>
+      </c>
       <c r="Q269" t="b">
         <v>0</v>
       </c>
@@ -17192,6 +20182,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P270" t="n">
+        <v>52</v>
+      </c>
       <c r="Q270" t="b">
         <v>0</v>
       </c>
@@ -17316,6 +20319,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P272" t="n">
+        <v>64</v>
+      </c>
       <c r="Q272" t="b">
         <v>0</v>
       </c>
@@ -17378,6 +20394,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P273" t="n">
+        <v>50</v>
+      </c>
       <c r="Q273" t="b">
         <v>0</v>
       </c>
@@ -17440,6 +20469,19 @@
           <t>HIMJKP</t>
         </is>
       </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P274" t="n">
+        <v>34</v>
+      </c>
       <c r="Q274" t="b">
         <v>0</v>
       </c>
@@ -17502,6 +20544,19 @@
           <t>RTRYDVBHMP</t>
         </is>
       </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P275" t="n">
+        <v>43</v>
+      </c>
       <c r="Q275" t="b">
         <v>0</v>
       </c>
@@ -17564,8 +20619,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P276" t="n">
+        <v>58</v>
+      </c>
       <c r="Q276" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R276" t="n">
         <v>45</v>
@@ -17626,6 +20694,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P277" t="n">
+        <v>55</v>
+      </c>
       <c r="Q277" t="b">
         <v>0</v>
       </c>
@@ -17688,6 +20769,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P278" t="n">
+        <v>31</v>
+      </c>
       <c r="Q278" t="b">
         <v>0</v>
       </c>
@@ -17750,6 +20844,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P279" t="n">
+        <v>63</v>
+      </c>
       <c r="Q279" t="b">
         <v>0</v>
       </c>
@@ -17874,6 +20981,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P281" t="n">
+        <v>47</v>
+      </c>
       <c r="Q281" t="b">
         <v>0</v>
       </c>
@@ -17936,6 +21056,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P282" t="n">
+        <v>51</v>
+      </c>
       <c r="Q282" t="b">
         <v>0</v>
       </c>
@@ -17998,6 +21131,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P283" t="n">
+        <v>41</v>
+      </c>
       <c r="Q283" t="b">
         <v>0</v>
       </c>
@@ -18060,8 +21206,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P284" t="n">
+        <v>59</v>
+      </c>
       <c r="Q284" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R284" t="n">
         <v>45</v>
@@ -18122,6 +21281,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P285" t="n">
+        <v>45</v>
+      </c>
       <c r="Q285" t="b">
         <v>0</v>
       </c>
@@ -18246,6 +21418,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P287" t="n">
+        <v>40</v>
+      </c>
       <c r="Q287" t="b">
         <v>0</v>
       </c>
@@ -18308,6 +21493,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P288" t="n">
+        <v>48</v>
+      </c>
       <c r="Q288" t="b">
         <v>0</v>
       </c>
@@ -18370,6 +21568,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P289" t="n">
+        <v>28</v>
+      </c>
       <c r="Q289" t="b">
         <v>0</v>
       </c>
@@ -18432,8 +21643,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P290" t="n">
+        <v>57</v>
+      </c>
       <c r="Q290" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R290" t="n">
         <v>45</v>
@@ -18556,6 +21780,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P292" t="n">
+        <v>62</v>
+      </c>
       <c r="Q292" t="b">
         <v>0</v>
       </c>
@@ -18618,6 +21855,19 @@
           <t>RTRYDVBHMP</t>
         </is>
       </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P293" t="n">
+        <v>38</v>
+      </c>
       <c r="Q293" t="b">
         <v>0</v>
       </c>
@@ -18680,6 +21930,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P294" t="n">
+        <v>57</v>
+      </c>
       <c r="Q294" t="b">
         <v>0</v>
       </c>
@@ -18742,6 +22005,19 @@
           <t>HIMJKP</t>
         </is>
       </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P295" t="n">
+        <v>65</v>
+      </c>
       <c r="Q295" t="b">
         <v>0</v>
       </c>
@@ -18804,8 +22080,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P296" t="n">
+        <v>61</v>
+      </c>
       <c r="Q296" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R296" t="n">
         <v>45</v>
@@ -18866,6 +22155,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P297" t="n">
+        <v>53</v>
+      </c>
       <c r="Q297" t="b">
         <v>0</v>
       </c>
@@ -18928,6 +22230,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P298" t="n">
+        <v>51</v>
+      </c>
       <c r="Q298" t="b">
         <v>0</v>
       </c>
@@ -18990,6 +22305,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P299" t="n">
+        <v>39</v>
+      </c>
       <c r="Q299" t="b">
         <v>0</v>
       </c>
@@ -19052,6 +22380,19 @@
           <t>RTRYDVBHMP</t>
         </is>
       </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P300" t="n">
+        <v>49</v>
+      </c>
       <c r="Q300" t="b">
         <v>0</v>
       </c>
@@ -19176,6 +22517,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P302" t="n">
+        <v>58</v>
+      </c>
       <c r="Q302" t="b">
         <v>0</v>
       </c>
@@ -19238,8 +22592,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P303" t="n">
+        <v>52</v>
+      </c>
       <c r="Q303" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R303" t="n">
         <v>45</v>
@@ -19300,6 +22667,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P304" t="n">
+        <v>42</v>
+      </c>
       <c r="Q304" t="b">
         <v>0</v>
       </c>
@@ -19362,6 +22742,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P305" t="n">
+        <v>71</v>
+      </c>
       <c r="Q305" t="b">
         <v>0</v>
       </c>
@@ -19486,6 +22879,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P307" t="n">
+        <v>37</v>
+      </c>
       <c r="Q307" t="b">
         <v>0</v>
       </c>
@@ -19548,6 +22954,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P308" t="n">
+        <v>33</v>
+      </c>
       <c r="Q308" t="b">
         <v>0</v>
       </c>
@@ -19610,6 +23029,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P309" t="n">
+        <v>49</v>
+      </c>
       <c r="Q309" t="b">
         <v>0</v>
       </c>
@@ -19672,8 +23104,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P310" t="n">
+        <v>58</v>
+      </c>
       <c r="Q310" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R310" t="n">
         <v>45</v>
@@ -19734,6 +23179,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P311" t="n">
+        <v>39</v>
+      </c>
       <c r="Q311" t="b">
         <v>0</v>
       </c>
@@ -19858,6 +23316,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P313" t="n">
+        <v>67</v>
+      </c>
       <c r="Q313" t="b">
         <v>0</v>
       </c>
@@ -19920,8 +23391,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P314" t="n">
+        <v>66</v>
+      </c>
       <c r="Q314" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R314" t="n">
         <v>45</v>
@@ -19982,6 +23466,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P315" t="n">
+        <v>41</v>
+      </c>
       <c r="Q315" t="b">
         <v>0</v>
       </c>
@@ -20044,6 +23541,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P316" t="n">
+        <v>51</v>
+      </c>
       <c r="Q316" t="b">
         <v>0</v>
       </c>
@@ -20106,6 +23616,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P317" t="n">
+        <v>38</v>
+      </c>
       <c r="Q317" t="b">
         <v>0</v>
       </c>
@@ -20168,6 +23691,19 @@
           <t>RTRYDVBHMP</t>
         </is>
       </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P318" t="n">
+        <v>55</v>
+      </c>
       <c r="Q318" t="b">
         <v>0</v>
       </c>
@@ -20292,6 +23828,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P320" t="n">
+        <v>61</v>
+      </c>
       <c r="Q320" t="b">
         <v>0</v>
       </c>
@@ -20354,6 +23903,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P321" t="n">
+        <v>48</v>
+      </c>
       <c r="Q321" t="b">
         <v>0</v>
       </c>
@@ -20416,6 +23978,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P322" t="n">
+        <v>50</v>
+      </c>
       <c r="Q322" t="b">
         <v>0</v>
       </c>
@@ -20478,8 +24053,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P323" t="n">
+        <v>56</v>
+      </c>
       <c r="Q323" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R323" t="n">
         <v>45</v>
@@ -20540,6 +24128,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P324" t="n">
+        <v>57</v>
+      </c>
       <c r="Q324" t="b">
         <v>0</v>
       </c>
@@ -20602,6 +24203,19 @@
           <t>RTRYDVBHMP</t>
         </is>
       </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P325" t="n">
+        <v>42</v>
+      </c>
       <c r="Q325" t="b">
         <v>0</v>
       </c>
@@ -20664,6 +24278,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P326" t="n">
+        <v>67</v>
+      </c>
       <c r="Q326" t="b">
         <v>0</v>
       </c>
@@ -20788,6 +24415,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P328" t="n">
+        <v>49</v>
+      </c>
       <c r="Q328" t="b">
         <v>0</v>
       </c>
@@ -20850,6 +24490,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P329" t="n">
+        <v>35</v>
+      </c>
       <c r="Q329" t="b">
         <v>0</v>
       </c>
@@ -20912,6 +24565,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P330" t="n">
+        <v>63</v>
+      </c>
       <c r="Q330" t="b">
         <v>0</v>
       </c>
@@ -20974,6 +24640,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P331" t="n">
+        <v>48</v>
+      </c>
       <c r="Q331" t="b">
         <v>0</v>
       </c>
@@ -21036,6 +24715,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P332" t="n">
+        <v>55</v>
+      </c>
       <c r="Q332" t="b">
         <v>0</v>
       </c>
@@ -21098,6 +24790,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P333" t="n">
+        <v>51</v>
+      </c>
       <c r="Q333" t="b">
         <v>0</v>
       </c>
@@ -21160,6 +24865,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P334" t="n">
+        <v>49</v>
+      </c>
       <c r="Q334" t="b">
         <v>0</v>
       </c>
@@ -21222,6 +24940,19 @@
           <t>RTRYDVBHMP</t>
         </is>
       </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P335" t="n">
+        <v>44</v>
+      </c>
       <c r="Q335" t="b">
         <v>0</v>
       </c>
@@ -21284,6 +25015,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P336" t="n">
+        <v>60</v>
+      </c>
       <c r="Q336" t="b">
         <v>0</v>
       </c>
@@ -21408,6 +25152,19 @@
           <t>SWAP</t>
         </is>
       </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P338" t="n">
+        <v>47</v>
+      </c>
       <c r="Q338" t="b">
         <v>0</v>
       </c>
@@ -21470,6 +25227,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P339" t="n">
+        <v>47</v>
+      </c>
       <c r="Q339" t="b">
         <v>0</v>
       </c>
@@ -21532,6 +25302,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P340" t="n">
+        <v>26</v>
+      </c>
       <c r="Q340" t="b">
         <v>0</v>
       </c>
@@ -21594,6 +25377,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P341" t="n">
+        <v>58</v>
+      </c>
       <c r="Q341" t="b">
         <v>0</v>
       </c>
@@ -21656,8 +25452,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P342" t="n">
+        <v>71</v>
+      </c>
       <c r="Q342" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R342" t="n">
         <v>45</v>
@@ -21718,6 +25527,19 @@
           <t>RTRYDVBHMP</t>
         </is>
       </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P343" t="n">
+        <v>33</v>
+      </c>
       <c r="Q343" t="b">
         <v>0</v>
       </c>
@@ -21780,6 +25602,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P344" t="n">
+        <v>41</v>
+      </c>
       <c r="Q344" t="b">
         <v>0</v>
       </c>
@@ -21842,6 +25677,19 @@
           <t>CPI</t>
         </is>
       </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P345" t="n">
+        <v>62</v>
+      </c>
       <c r="Q345" t="b">
         <v>0</v>
       </c>
@@ -21966,6 +25814,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P347" t="n">
+        <v>57</v>
+      </c>
       <c r="Q347" t="b">
         <v>0</v>
       </c>
@@ -22028,6 +25889,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P348" t="n">
+        <v>53</v>
+      </c>
       <c r="Q348" t="b">
         <v>0</v>
       </c>
@@ -22090,6 +25964,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P349" t="n">
+        <v>66</v>
+      </c>
       <c r="Q349" t="b">
         <v>0</v>
       </c>
@@ -22152,6 +26039,19 @@
           <t>RTRYDVBHMP</t>
         </is>
       </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P350" t="n">
+        <v>42</v>
+      </c>
       <c r="Q350" t="b">
         <v>0</v>
       </c>
@@ -22276,6 +26176,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P352" t="n">
+        <v>40</v>
+      </c>
       <c r="Q352" t="b">
         <v>0</v>
       </c>
@@ -22338,6 +26251,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P353" t="n">
+        <v>28</v>
+      </c>
       <c r="Q353" t="b">
         <v>0</v>
       </c>
@@ -22400,6 +26326,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P354" t="n">
+        <v>40</v>
+      </c>
       <c r="Q354" t="b">
         <v>0</v>
       </c>
@@ -22462,6 +26401,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P355" t="n">
+        <v>62</v>
+      </c>
       <c r="Q355" t="b">
         <v>0</v>
       </c>
@@ -22524,6 +26476,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P356" t="n">
+        <v>43</v>
+      </c>
       <c r="Q356" t="b">
         <v>0</v>
       </c>
@@ -22586,6 +26551,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P357" t="n">
+        <v>54</v>
+      </c>
       <c r="Q357" t="b">
         <v>0</v>
       </c>
@@ -22648,6 +26626,19 @@
           <t>RTRYDVBHMP</t>
         </is>
       </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P358" t="n">
+        <v>37</v>
+      </c>
       <c r="Q358" t="b">
         <v>0</v>
       </c>
@@ -22710,6 +26701,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P359" t="n">
+        <v>49</v>
+      </c>
       <c r="Q359" t="b">
         <v>0</v>
       </c>
@@ -22834,6 +26838,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P361" t="n">
+        <v>40</v>
+      </c>
       <c r="Q361" t="b">
         <v>0</v>
       </c>
@@ -22896,6 +26913,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P362" t="n">
+        <v>41</v>
+      </c>
       <c r="Q362" t="b">
         <v>0</v>
       </c>
@@ -22958,6 +26988,19 @@
           <t>SWAP</t>
         </is>
       </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P363" t="n">
+        <v>45</v>
+      </c>
       <c r="Q363" t="b">
         <v>0</v>
       </c>
@@ -23020,6 +27063,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P364" t="n">
+        <v>53</v>
+      </c>
       <c r="Q364" t="b">
         <v>0</v>
       </c>
@@ -23082,6 +27138,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P365" t="n">
+        <v>57</v>
+      </c>
       <c r="Q365" t="b">
         <v>0</v>
       </c>
@@ -23144,6 +27213,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P366" t="n">
+        <v>48</v>
+      </c>
       <c r="Q366" t="b">
         <v>0</v>
       </c>
@@ -23206,6 +27288,19 @@
           <t>RTRYDVBHMP</t>
         </is>
       </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P367" t="n">
+        <v>53</v>
+      </c>
       <c r="Q367" t="b">
         <v>0</v>
       </c>
@@ -23268,6 +27363,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P368" t="n">
+        <v>55</v>
+      </c>
       <c r="Q368" t="b">
         <v>0</v>
       </c>
@@ -23330,6 +27438,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P369" t="n">
+        <v>34</v>
+      </c>
       <c r="Q369" t="b">
         <v>0</v>
       </c>
@@ -23454,8 +27575,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P371" t="n">
+        <v>82</v>
+      </c>
       <c r="Q371" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R371" t="n">
         <v>45</v>
@@ -23516,6 +27650,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P372" t="n">
+        <v>59</v>
+      </c>
       <c r="Q372" t="b">
         <v>0</v>
       </c>
@@ -23578,6 +27725,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P373" t="n">
+        <v>41</v>
+      </c>
       <c r="Q373" t="b">
         <v>0</v>
       </c>
@@ -23702,6 +27862,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P375" t="n">
+        <v>58</v>
+      </c>
       <c r="Q375" t="b">
         <v>0</v>
       </c>
@@ -23764,6 +27937,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P376" t="n">
+        <v>40</v>
+      </c>
       <c r="Q376" t="b">
         <v>0</v>
       </c>
@@ -23826,8 +28012,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P377" t="n">
+        <v>51</v>
+      </c>
       <c r="Q377" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R377" t="n">
         <v>45</v>
@@ -23888,6 +28087,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P378" t="n">
+        <v>59</v>
+      </c>
       <c r="Q378" t="b">
         <v>0</v>
       </c>
@@ -23950,6 +28162,19 @@
           <t>RTRYDVBHMP</t>
         </is>
       </c>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P379" t="n">
+        <v>41</v>
+      </c>
       <c r="Q379" t="b">
         <v>0</v>
       </c>
@@ -24074,6 +28299,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P381" t="n">
+        <v>41</v>
+      </c>
       <c r="Q381" t="b">
         <v>0</v>
       </c>
@@ -24136,6 +28374,19 @@
           <t>HIMJKP</t>
         </is>
       </c>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P382" t="n">
+        <v>57</v>
+      </c>
       <c r="Q382" t="b">
         <v>0</v>
       </c>
@@ -24198,6 +28449,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P383" t="n">
+        <v>64</v>
+      </c>
       <c r="Q383" t="b">
         <v>0</v>
       </c>
@@ -24260,6 +28524,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P384" t="n">
+        <v>38</v>
+      </c>
       <c r="Q384" t="b">
         <v>0</v>
       </c>
@@ -24322,6 +28599,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P385" t="n">
+        <v>43</v>
+      </c>
       <c r="Q385" t="b">
         <v>0</v>
       </c>
@@ -24384,6 +28674,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P386" t="n">
+        <v>77</v>
+      </c>
       <c r="Q386" t="b">
         <v>0</v>
       </c>
@@ -24446,6 +28749,19 @@
           <t>RTRYDVBHMP</t>
         </is>
       </c>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P387" t="n">
+        <v>55</v>
+      </c>
       <c r="Q387" t="b">
         <v>0</v>
       </c>
@@ -24508,6 +28824,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P388" t="n">
+        <v>40</v>
+      </c>
       <c r="Q388" t="b">
         <v>0</v>
       </c>
@@ -24570,6 +28899,19 @@
           <t>CPI(M)</t>
         </is>
       </c>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P389" t="n">
+        <v>40</v>
+      </c>
       <c r="Q389" t="b">
         <v>0</v>
       </c>
@@ -24694,6 +29036,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P391" t="n">
+        <v>51</v>
+      </c>
       <c r="Q391" t="b">
         <v>0</v>
       </c>
@@ -24756,8 +29111,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P392" t="n">
+        <v>67</v>
+      </c>
       <c r="Q392" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R392" t="n">
         <v>45</v>
@@ -24880,6 +29248,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P394" t="n">
+        <v>40</v>
+      </c>
       <c r="Q394" t="b">
         <v>0</v>
       </c>
@@ -24942,6 +29323,19 @@
           <t>RTRYDVBHMP</t>
         </is>
       </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P395" t="n">
+        <v>37</v>
+      </c>
       <c r="Q395" t="b">
         <v>0</v>
       </c>
@@ -25004,6 +29398,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P396" t="n">
+        <v>58</v>
+      </c>
       <c r="Q396" t="b">
         <v>0</v>
       </c>
@@ -25066,6 +29473,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P397" t="n">
+        <v>34</v>
+      </c>
       <c r="Q397" t="b">
         <v>0</v>
       </c>
@@ -25128,8 +29548,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P398" t="n">
+        <v>44</v>
+      </c>
       <c r="Q398" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R398" t="n">
         <v>45</v>
@@ -25190,6 +29623,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P399" t="n">
+        <v>56</v>
+      </c>
       <c r="Q399" t="b">
         <v>0</v>
       </c>
@@ -25252,6 +29698,19 @@
           <t>RTRYDVBHMP</t>
         </is>
       </c>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P400" t="n">
+        <v>55</v>
+      </c>
       <c r="Q400" t="b">
         <v>0</v>
       </c>
@@ -25314,6 +29773,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P401" t="n">
+        <v>59</v>
+      </c>
       <c r="Q401" t="b">
         <v>0</v>
       </c>
@@ -25438,6 +29910,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P403" t="n">
+        <v>58</v>
+      </c>
       <c r="Q403" t="b">
         <v>0</v>
       </c>
@@ -25500,6 +29985,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P404" t="n">
+        <v>65</v>
+      </c>
       <c r="Q404" t="b">
         <v>0</v>
       </c>
@@ -25562,6 +30060,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P405" t="n">
+        <v>42</v>
+      </c>
       <c r="Q405" t="b">
         <v>0</v>
       </c>
@@ -25624,6 +30135,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P406" t="n">
+        <v>47</v>
+      </c>
       <c r="Q406" t="b">
         <v>0</v>
       </c>
@@ -25686,6 +30210,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P407" t="n">
+        <v>57</v>
+      </c>
       <c r="Q407" t="b">
         <v>0</v>
       </c>
@@ -25748,6 +30285,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P408" t="n">
+        <v>39</v>
+      </c>
       <c r="Q408" t="b">
         <v>0</v>
       </c>
@@ -25872,6 +30422,19 @@
           <t>RTRYDVBHMP</t>
         </is>
       </c>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P410" t="n">
+        <v>58</v>
+      </c>
       <c r="Q410" t="b">
         <v>0</v>
       </c>
@@ -25934,6 +30497,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P411" t="n">
+        <v>60</v>
+      </c>
       <c r="Q411" t="b">
         <v>0</v>
       </c>
@@ -25996,6 +30572,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P412" t="n">
+        <v>38</v>
+      </c>
       <c r="Q412" t="b">
         <v>0</v>
       </c>
@@ -26058,8 +30647,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P413" t="n">
+        <v>58</v>
+      </c>
       <c r="Q413" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R413" t="n">
         <v>45</v>
@@ -26120,6 +30722,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P414" t="n">
+        <v>51</v>
+      </c>
       <c r="Q414" t="b">
         <v>0</v>
       </c>
@@ -26244,6 +30859,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P416" t="n">
+        <v>44</v>
+      </c>
       <c r="Q416" t="b">
         <v>0</v>
       </c>
@@ -26306,6 +30934,19 @@
           <t>RTRYDVBHMP</t>
         </is>
       </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P417" t="n">
+        <v>41</v>
+      </c>
       <c r="Q417" t="b">
         <v>0</v>
       </c>
@@ -26368,8 +31009,21 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P418" t="n">
+        <v>52</v>
+      </c>
       <c r="Q418" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R418" t="n">
         <v>45</v>
@@ -26430,6 +31084,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P419" t="n">
+        <v>49</v>
+      </c>
       <c r="Q419" t="b">
         <v>0</v>
       </c>
@@ -26492,6 +31159,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P420" t="n">
+        <v>50</v>
+      </c>
       <c r="Q420" t="b">
         <v>0</v>
       </c>
@@ -26616,6 +31296,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P422" t="n">
+        <v>41</v>
+      </c>
       <c r="Q422" t="b">
         <v>0</v>
       </c>
@@ -26678,6 +31371,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P423" t="n">
+        <v>45</v>
+      </c>
       <c r="Q423" t="b">
         <v>0</v>
       </c>
@@ -26740,6 +31446,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P424" t="n">
+        <v>41</v>
+      </c>
       <c r="Q424" t="b">
         <v>0</v>
       </c>
@@ -26802,6 +31521,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P425" t="n">
+        <v>62</v>
+      </c>
       <c r="Q425" t="b">
         <v>0</v>
       </c>
@@ -26864,6 +31596,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P426" t="n">
+        <v>40</v>
+      </c>
       <c r="Q426" t="b">
         <v>0</v>
       </c>
@@ -26926,6 +31671,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P427" t="n">
+        <v>60</v>
+      </c>
       <c r="Q427" t="b">
         <v>0</v>
       </c>
@@ -26988,6 +31746,19 @@
           <t>CPI(M)</t>
         </is>
       </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P428" t="n">
+        <v>66</v>
+      </c>
       <c r="Q428" t="b">
         <v>0</v>
       </c>
@@ -27050,6 +31821,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P429" t="n">
+        <v>65</v>
+      </c>
       <c r="Q429" t="b">
         <v>0</v>
       </c>
@@ -27112,6 +31896,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P430" t="n">
+        <v>38</v>
+      </c>
       <c r="Q430" t="b">
         <v>0</v>
       </c>
@@ -27174,6 +31971,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P431" t="n">
+        <v>69</v>
+      </c>
       <c r="Q431" t="b">
         <v>0</v>
       </c>
@@ -27298,6 +32108,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P433" t="n">
+        <v>61</v>
+      </c>
       <c r="Q433" t="b">
         <v>0</v>
       </c>
@@ -27360,8 +32183,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P434" t="n">
+        <v>45</v>
+      </c>
       <c r="Q434" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R434" t="n">
         <v>45</v>
@@ -27422,6 +32258,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P435" t="n">
+        <v>70</v>
+      </c>
       <c r="Q435" t="b">
         <v>0</v>
       </c>
@@ -27484,6 +32333,19 @@
           <t>CPI(M)</t>
         </is>
       </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P436" t="n">
+        <v>65</v>
+      </c>
       <c r="Q436" t="b">
         <v>0</v>
       </c>
@@ -27608,6 +32470,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P438" t="n">
+        <v>54</v>
+      </c>
       <c r="Q438" t="b">
         <v>0</v>
       </c>
@@ -27670,6 +32545,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P439" t="n">
+        <v>62</v>
+      </c>
       <c r="Q439" t="b">
         <v>0</v>
       </c>
@@ -27732,6 +32620,19 @@
           <t>RTRYDVBHMP</t>
         </is>
       </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P440" t="n">
+        <v>36</v>
+      </c>
       <c r="Q440" t="b">
         <v>0</v>
       </c>
@@ -27794,6 +32695,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P441" t="n">
+        <v>57</v>
+      </c>
       <c r="Q441" t="b">
         <v>0</v>
       </c>
@@ -27856,6 +32770,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P442" t="n">
+        <v>57</v>
+      </c>
       <c r="Q442" t="b">
         <v>0</v>
       </c>
@@ -27918,6 +32845,19 @@
           <t>CPI(M)</t>
         </is>
       </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P443" t="n">
+        <v>50</v>
+      </c>
       <c r="Q443" t="b">
         <v>0</v>
       </c>
@@ -27980,6 +32920,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P444" t="n">
+        <v>52</v>
+      </c>
       <c r="Q444" t="b">
         <v>0</v>
       </c>
@@ -28104,6 +33057,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P446" t="n">
+        <v>38</v>
+      </c>
       <c r="Q446" t="b">
         <v>0</v>
       </c>
@@ -28166,6 +33132,19 @@
           <t>RTRYDVBHMP</t>
         </is>
       </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P447" t="n">
+        <v>38</v>
+      </c>
       <c r="Q447" t="b">
         <v>0</v>
       </c>
@@ -28228,6 +33207,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P448" t="n">
+        <v>56</v>
+      </c>
       <c r="Q448" t="b">
         <v>0</v>
       </c>
@@ -28290,8 +33282,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P449" t="n">
+        <v>33</v>
+      </c>
       <c r="Q449" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R449" t="n">
         <v>45</v>
@@ -28352,6 +33357,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P450" t="n">
+        <v>50</v>
+      </c>
       <c r="Q450" t="b">
         <v>0</v>
       </c>
@@ -28414,6 +33432,19 @@
           <t>RTRYDVBHMP</t>
         </is>
       </c>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P451" t="n">
+        <v>42</v>
+      </c>
       <c r="Q451" t="b">
         <v>0</v>
       </c>
@@ -28538,6 +33569,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P453" t="n">
+        <v>45</v>
+      </c>
       <c r="Q453" t="b">
         <v>0</v>
       </c>
@@ -28600,6 +33644,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P454" t="n">
+        <v>56</v>
+      </c>
       <c r="Q454" t="b">
         <v>0</v>
       </c>
@@ -28662,6 +33719,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P455" t="n">
+        <v>38</v>
+      </c>
       <c r="Q455" t="b">
         <v>0</v>
       </c>
@@ -28724,6 +33794,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P456" t="n">
+        <v>48</v>
+      </c>
       <c r="Q456" t="b">
         <v>0</v>
       </c>
@@ -28786,6 +33869,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P457" t="n">
+        <v>45</v>
+      </c>
       <c r="Q457" t="b">
         <v>0</v>
       </c>
@@ -28848,6 +33944,19 @@
           <t>CPI(M)</t>
         </is>
       </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P458" t="n">
+        <v>51</v>
+      </c>
       <c r="Q458" t="b">
         <v>0</v>
       </c>
@@ -28910,6 +34019,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P459" t="n">
+        <v>37</v>
+      </c>
       <c r="Q459" t="b">
         <v>0</v>
       </c>
@@ -29034,6 +34156,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P461" t="n">
+        <v>38</v>
+      </c>
       <c r="Q461" t="b">
         <v>0</v>
       </c>
@@ -29096,6 +34231,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P462" t="n">
+        <v>34</v>
+      </c>
       <c r="Q462" t="b">
         <v>0</v>
       </c>
@@ -29158,8 +34306,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P463" t="n">
+        <v>68</v>
+      </c>
       <c r="Q463" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R463" t="n">
         <v>45</v>
@@ -29220,6 +34381,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P464" t="n">
+        <v>37</v>
+      </c>
       <c r="Q464" t="b">
         <v>0</v>
       </c>
@@ -29282,6 +34456,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P465" t="n">
+        <v>47</v>
+      </c>
       <c r="Q465" t="b">
         <v>0</v>
       </c>
@@ -29344,6 +34531,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N466" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P466" t="n">
+        <v>34</v>
+      </c>
       <c r="Q466" t="b">
         <v>0</v>
       </c>
@@ -29468,6 +34668,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N468" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O468" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P468" t="n">
+        <v>56</v>
+      </c>
       <c r="Q468" t="b">
         <v>0</v>
       </c>
@@ -29530,8 +34743,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N469" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P469" t="n">
+        <v>57</v>
+      </c>
       <c r="Q469" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R469" t="n">
         <v>45</v>
@@ -29592,6 +34818,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N470" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P470" t="n">
+        <v>40</v>
+      </c>
       <c r="Q470" t="b">
         <v>0</v>
       </c>
@@ -29654,6 +34893,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N471" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O471" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P471" t="n">
+        <v>50</v>
+      </c>
       <c r="Q471" t="b">
         <v>0</v>
       </c>
@@ -29716,6 +34968,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N472" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P472" t="n">
+        <v>31</v>
+      </c>
       <c r="Q472" t="b">
         <v>0</v>
       </c>
@@ -29778,6 +35043,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N473" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P473" t="n">
+        <v>54</v>
+      </c>
       <c r="Q473" t="b">
         <v>0</v>
       </c>
@@ -29902,6 +35180,19 @@
           <t>RTRYDVBHMP</t>
         </is>
       </c>
+      <c r="N475" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O475" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P475" t="n">
+        <v>36</v>
+      </c>
       <c r="Q475" t="b">
         <v>0</v>
       </c>
@@ -29964,8 +35255,21 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N476" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O476" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P476" t="n">
+        <v>65</v>
+      </c>
       <c r="Q476" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R476" t="n">
         <v>45</v>
@@ -30026,6 +35330,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N477" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O477" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P477" t="n">
+        <v>50</v>
+      </c>
       <c r="Q477" t="b">
         <v>0</v>
       </c>
@@ -30088,6 +35405,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N478" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O478" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P478" t="n">
+        <v>61</v>
+      </c>
       <c r="Q478" t="b">
         <v>0</v>
       </c>
@@ -30150,6 +35480,19 @@
           <t>AAAP</t>
         </is>
       </c>
+      <c r="N479" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O479" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P479" t="n">
+        <v>38</v>
+      </c>
       <c r="Q479" t="b">
         <v>0</v>
       </c>
@@ -30211,6 +35554,19 @@
         <is>
           <t>BSP</t>
         </is>
+      </c>
+      <c r="N480" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O480" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P480" t="n">
+        <v>34</v>
       </c>
       <c r="Q480" t="b">
         <v>0</v>
